--- a/14.xlsx
+++ b/14.xlsx
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>9.747899999638321e-06</v>
+        <v>2.987010000015289e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>4.630499999620952e-06</v>
+        <v>5.179599999792117e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>4.992300000594696e-06</v>
+        <v>4.920299999866984e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>4.700400000729133e-06</v>
+        <v>5.011300000660413e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>5.053900000348221e-06</v>
+        <v>4.890500000328757e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.0980999985768e-06</v>
+        <v>5.4971999998088e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>5.323400000634138e-06</v>
+        <v>5.119399999784946e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.217499998252606e-06</v>
+        <v>4.85240000034537e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>4.781999999977416e-06</v>
+        <v>4.440699999577191e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>5.107600001792889e-06</v>
+        <v>6.277499999669089e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>4.653399999369867e-06</v>
+        <v>6.082099999730417e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>5.395099997258512e-06</v>
+        <v>5.33240000004298e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>4.965800002537435e-06</v>
+        <v>4.519600000094215e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>4.94510000135051e-06</v>
+        <v>5.274699999972654e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>5.015099999582163e-06</v>
+        <v>4.737799999929848e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>5.899600000702776e-06</v>
+        <v>5.331000000296626e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.079999999201391e-06</v>
+        <v>6.446399999731512e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>6.407600001693936e-06</v>
+        <v>5.952100000286009e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>6.123099999967963e-06</v>
+        <v>5.750199999965844e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>5.820200000016485e-06</v>
+        <v>5.323200000020734e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>5.373299998609582e-06</v>
+        <v>5.82269999995333e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>6.289299999480136e-06</v>
+        <v>5.94849999924918e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>6.022100002155639e-06</v>
+        <v>5.293399999573012e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>6.158600001072045e-06</v>
+        <v>5.892899999707879e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>5.690399997547501e-06</v>
+        <v>5.71490000038466e-06</v>
       </c>
     </row>
   </sheetData>
